--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>136547054</v>
       </c>
       <c r="B5" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136547291</v>
       </c>
       <c r="B6" t="n">
-        <v>99366</v>
+        <v>99369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136543880</v>
       </c>
       <c r="B7" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136546135</v>
       </c>
       <c r="B8" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136546304</v>
       </c>
       <c r="B9" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>136546390</v>
       </c>
       <c r="B10" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1649,7 +1649,7 @@
         <v>136546437</v>
       </c>
       <c r="B11" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136546806</v>
       </c>
       <c r="B12" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136547038</v>
       </c>
       <c r="B13" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136549238</v>
       </c>
       <c r="B14" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>136549993</v>
       </c>
       <c r="B15" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>136547054</v>
       </c>
       <c r="B5" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136547291</v>
       </c>
       <c r="B6" t="n">
-        <v>99369</v>
+        <v>99370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136543880</v>
       </c>
       <c r="B7" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136546135</v>
       </c>
       <c r="B8" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136546304</v>
       </c>
       <c r="B9" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>136546390</v>
       </c>
       <c r="B10" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1649,7 +1649,7 @@
         <v>136546437</v>
       </c>
       <c r="B11" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136546806</v>
       </c>
       <c r="B12" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136547038</v>
       </c>
       <c r="B13" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136549238</v>
       </c>
       <c r="B14" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>136549993</v>
       </c>
       <c r="B15" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542821</v>
       </c>
       <c r="B2" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136547434</v>
       </c>
       <c r="B3" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136547770</v>
       </c>
       <c r="B4" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136547054</v>
       </c>
       <c r="B5" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136547291</v>
       </c>
       <c r="B6" t="n">
-        <v>99370</v>
+        <v>99375</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136543880</v>
       </c>
       <c r="B7" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136546135</v>
       </c>
       <c r="B8" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136546304</v>
       </c>
       <c r="B9" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>136546390</v>
       </c>
       <c r="B10" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>136546437</v>
       </c>
       <c r="B11" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136546806</v>
       </c>
       <c r="B12" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136547038</v>
       </c>
       <c r="B13" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136549238</v>
       </c>
       <c r="B14" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>136549993</v>
       </c>
       <c r="B15" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>136547054</v>
       </c>
       <c r="B5" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136547291</v>
       </c>
       <c r="B6" t="n">
-        <v>99375</v>
+        <v>99377</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136543880</v>
       </c>
       <c r="B7" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136546135</v>
       </c>
       <c r="B8" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136546304</v>
       </c>
       <c r="B9" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>136546390</v>
       </c>
       <c r="B10" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>136546437</v>
       </c>
       <c r="B11" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136546806</v>
       </c>
       <c r="B12" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136547038</v>
       </c>
       <c r="B13" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136549238</v>
       </c>
       <c r="B14" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>136549993</v>
       </c>
       <c r="B15" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">

--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">

--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">

--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">

--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1013,7 +1013,7 @@
         <v>136547054</v>
       </c>
       <c r="B5" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136547291</v>
       </c>
       <c r="B6" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136543880</v>
       </c>
       <c r="B7" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136546135</v>
       </c>
       <c r="B8" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136546304</v>
       </c>
       <c r="B9" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>136546390</v>
       </c>
       <c r="B10" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1649,7 +1649,7 @@
         <v>136546437</v>
       </c>
       <c r="B11" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1755,7 +1755,7 @@
         <v>136546806</v>
       </c>
       <c r="B12" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136547038</v>
       </c>
       <c r="B13" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136549238</v>
       </c>
       <c r="B14" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>136549993</v>
       </c>
       <c r="B15" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1013,7 +1013,7 @@
         <v>136547054</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136547291</v>
       </c>
       <c r="B6" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136543880</v>
       </c>
       <c r="B7" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136546135</v>
       </c>
       <c r="B8" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136546304</v>
       </c>
       <c r="B9" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>136546390</v>
       </c>
       <c r="B10" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1649,7 +1649,7 @@
         <v>136546437</v>
       </c>
       <c r="B11" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1755,7 +1755,7 @@
         <v>136546806</v>
       </c>
       <c r="B12" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136547038</v>
       </c>
       <c r="B13" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136549238</v>
       </c>
       <c r="B14" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>136549993</v>
       </c>
       <c r="B15" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>136547054</v>
       </c>
       <c r="B5" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136547291</v>
       </c>
       <c r="B6" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136543880</v>
       </c>
       <c r="B7" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136546135</v>
       </c>
       <c r="B8" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136546304</v>
       </c>
       <c r="B9" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>136546390</v>
       </c>
       <c r="B10" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>136546437</v>
       </c>
       <c r="B11" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136546806</v>
       </c>
       <c r="B12" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136547038</v>
       </c>
       <c r="B13" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136549238</v>
       </c>
       <c r="B14" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>136549993</v>
       </c>
       <c r="B15" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>136547054</v>
       </c>
       <c r="B5" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136547291</v>
       </c>
       <c r="B6" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1225,7 +1225,7 @@
         <v>136543880</v>
       </c>
       <c r="B7" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136546135</v>
       </c>
       <c r="B8" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136546304</v>
       </c>
       <c r="B9" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>136546390</v>
       </c>
       <c r="B10" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>136546437</v>
       </c>
       <c r="B11" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136546806</v>
       </c>
       <c r="B12" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136547038</v>
       </c>
       <c r="B13" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136549238</v>
       </c>
       <c r="B14" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>136549993</v>
       </c>
       <c r="B15" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>136547054</v>
       </c>
       <c r="B5" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136547291</v>
       </c>
       <c r="B6" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136543880</v>
       </c>
       <c r="B7" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136546135</v>
       </c>
       <c r="B8" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136546304</v>
       </c>
       <c r="B9" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>136546390</v>
       </c>
       <c r="B10" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>136546437</v>
       </c>
       <c r="B11" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136546806</v>
       </c>
       <c r="B12" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136547038</v>
       </c>
       <c r="B13" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136549238</v>
       </c>
       <c r="B14" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>136549993</v>
       </c>
       <c r="B15" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -1948,7 +1948,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">

--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>136547054</v>
       </c>
       <c r="B5" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136547291</v>
       </c>
       <c r="B6" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136543880</v>
       </c>
       <c r="B7" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136546135</v>
       </c>
       <c r="B8" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136546304</v>
       </c>
       <c r="B9" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>136546390</v>
       </c>
       <c r="B10" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>136546437</v>
       </c>
       <c r="B11" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136546806</v>
       </c>
       <c r="B12" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136547038</v>
       </c>
       <c r="B13" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1967,7 +1967,7 @@
         <v>136549238</v>
       </c>
       <c r="B14" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>136549993</v>
       </c>
       <c r="B15" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>136547054</v>
       </c>
       <c r="B5" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136547291</v>
       </c>
       <c r="B6" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1225,7 +1225,7 @@
         <v>136543880</v>
       </c>
       <c r="B7" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136546135</v>
       </c>
       <c r="B8" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136546304</v>
       </c>
       <c r="B9" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>136546390</v>
       </c>
       <c r="B10" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>136546437</v>
       </c>
       <c r="B11" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136546806</v>
       </c>
       <c r="B12" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136547038</v>
       </c>
       <c r="B13" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136549238</v>
       </c>
       <c r="B14" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>136549993</v>
       </c>
       <c r="B15" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542821</v>
       </c>
       <c r="B2" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136547434</v>
       </c>
       <c r="B3" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136547770</v>
       </c>
       <c r="B4" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136547054</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136547291</v>
       </c>
       <c r="B6" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1225,7 +1225,7 @@
         <v>136543880</v>
       </c>
       <c r="B7" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136546135</v>
       </c>
       <c r="B8" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136546304</v>
       </c>
       <c r="B9" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>136546390</v>
       </c>
       <c r="B10" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>136546437</v>
       </c>
       <c r="B11" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136546806</v>
       </c>
       <c r="B12" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136547038</v>
       </c>
       <c r="B13" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136549238</v>
       </c>
       <c r="B14" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>136549993</v>
       </c>
       <c r="B15" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24874-2024 artfynd.xlsx
+++ b/artfynd/A 24874-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542821</v>
       </c>
       <c r="B2" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136547434</v>
       </c>
       <c r="B3" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136547770</v>
       </c>
       <c r="B4" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136547054</v>
       </c>
       <c r="B5" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136547291</v>
       </c>
       <c r="B6" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>136543880</v>
       </c>
       <c r="B7" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136546135</v>
       </c>
       <c r="B8" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136546304</v>
       </c>
       <c r="B9" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>136546390</v>
       </c>
       <c r="B10" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>136546437</v>
       </c>
       <c r="B11" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>136546806</v>
       </c>
       <c r="B12" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>136547038</v>
       </c>
       <c r="B13" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>136549238</v>
       </c>
       <c r="B14" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>136549993</v>
       </c>
       <c r="B15" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
